--- a/Vanguard US/Vanguard-US-KostenBepaling.xlsx
+++ b/Vanguard US/Vanguard-US-KostenBepaling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Vanguard US/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1568" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73BE7F45-6B32-40B9-A0A7-BD155F328D0A}"/>
+  <xr:revisionPtr revIDLastSave="1581" documentId="13_ncr:1_{1145E7EB-B52A-4035-9DB0-6756A4D32375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{486BD9CB-BCEE-4EC0-BB99-04EA05503D5C}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,11 +356,11 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
-    <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="0.0000%"/>
-    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="0.0000%"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -472,23 +472,23 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -510,11 +510,11 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -522,6 +522,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -541,6 +542,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3074,9 +3079,11 @@
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="35"/>
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="35"/>
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
@@ -3509,7 +3516,7 @@
         <v>-0.32000000000000028</v>
       </c>
       <c r="C8" s="18">
-        <f t="shared" ref="C8:K8" si="2">C7-C6</f>
+        <f t="shared" ref="C8:J8" si="2">C7-C6</f>
         <v>0.74000000000000021</v>
       </c>
       <c r="D8" s="18">
